--- a/docs/qa/POS_FE_QA_ANALYSIS.xlsx
+++ b/docs/qa/POS_FE_QA_ANALYSIS.xlsx
@@ -28,12 +28,13 @@
     <sheet name="Motor-Fiscal" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Catálogos-DataApi" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Código-Huérfano" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Hallazgos" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Verticales-TipoNegocio" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Hallazgos" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Autenticación'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dashboard'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'POS-Documentos'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'POS-Documentos'!$A$1:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Facturación-Hacienda'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Productos'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Categorías'!$A$1:$F$2</definedName>
@@ -51,7 +52,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Motor-Fiscal'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Catálogos-DataApi'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Código-Huérfano'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Hallazgos'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Verticales-TipoNegocio'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Hallazgos'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -562,7 +564,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-07 (verticales por tipo de negocio)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -576,7 +578,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>65f2ca9 (main, sincronizada con remoto)</t>
+          <t>working tree (TSR-150…164 verticales)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -769,10 +771,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="n"/>
     </row>
@@ -968,7 +970,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n"/>
     </row>
@@ -1015,79 +1017,71 @@
       <c r="D36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Verticales-TipoNegocio</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="D37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Riesgos críticos (roadmap §6) que QA debe conocer</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Riesgos críticos (roadmap §6) que QA debe conocer</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>TSR</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Severidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Credenciales fiscales (P12, PIN, ATV) en texto plano en Postgres y retornadas por GET; realm OAuth hardcodeado a staging</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>TSR-002, TSR-003</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Crítica (legal)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Verdad fiscal duplicada: dos asignadores de consecutivo, tres motores de impuestos sincronizados 'por convención'</t>
+          <t>Credenciales fiscales (P12, PIN, ATV) en texto plano en Postgres y retornadas por GET; realm OAuth hardcodeado a staging</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TSR-004</t>
+          <t>TSR-002, TSR-003</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1099,42 +1093,64 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Gateway de markets-api no valida userId↔sub; el RBAC confía en una validación inexistente</t>
+          <t>Verdad fiscal duplicada: dos asignadores de consecutivo, tres motores de impuestos sincronizados 'por convención'</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TSR-029</t>
+          <t>TSR-004</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Crítica (seguridad)</t>
+          <t>Crítica (legal)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Gateway de markets-api no valida userId↔sub; el RBAC confía en una validación inexistente</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>TSR-029</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Crítica (seguridad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Servicios Python (sales/orders/data-api) sin checks de membresía; docs fiscales y credenciales ATV expuestos</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>TSR-030, TSR-031</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Crítica (seguridad)</t>
         </is>
@@ -2521,7 +2537,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Las fugas de i18n del TSR-119 se ven SOLO en EN</t>
+          <t>Fugas conocidas de documentos corregidas; mantener recorrido EN</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2538,12 +2554,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>useSync + Dexie (IndexedDB) para inventario, SyncPill en POSIntegratedPage; SW registrado (public/sw.js, PWA manifest)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>🟡 Parcial</t>
+          <t>Dexie v2 + PendingSalesSyncBridge autenticado; SyncPill online/offline/syncing/pending/error</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2553,7 +2569,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>El replay de ventas offline está ROTO (token nunca persistido); parte del flujo offline vive en código huérfano (TSR-120)</t>
+          <t>SW ya no reenvía ventas; validar reconexión, reinicio y aislamiento por usuario</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2629,17 +2645,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Impresión de recibo</t>
+          <t>Impresión de ticket 80 mm</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PRINT_RECEIPT.md documenta botón en src/pages/pos/POSPage.tsx — archivo que ya no existe</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>❌ Faltante</t>
+          <t>Ticket generado en el backend (ticket.html → wkhtmltopdf 72 mm → S3), expuesto en attachments.ticket_url</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2649,12 +2665,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Único window.print está en ReportePage; Receipt.tsx del checkout no imprime — no se puede imprimir recibo de venta</t>
+          <t>Regenera a propósito para tomar el consecutivo/QR tras facturar. Faltan comandas por estación</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2746,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Drawers móviles (nav, documentos), panel de notificaciones centrado, toolbar container-queries</t>
+          <t>Drawers móviles, panel de notificaciones centrado, toolbar container-queries</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2740,12 +2756,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>TSR-111</t>
+          <t>TSR-111, TSR-132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Drawers/modales usan portal + overlay stack; probar página scrolleada y overlays anidados</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3394,12 +3410,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TSR-008</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Password en sessionStorage post-OTP (XSS-legible) — TSR-008</t>
+          <t>Credenciales ya no se guardan en sessionStorage; elimina cualquier valor legacy</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3431,7 +3447,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Stash de password en sessionStorage</t>
+          <t>Verificación usa autoSignIn de Amplify sin persistir password</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3855,7 +3871,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>useAllEconomicActivities (lo que TSR-006 necesita), useAllExemptions/useExemptionValidation (TSR-124), useAllOtherCharges (TSR-125), useAllDocumentTypes, PharmaceuticalForms, Regimes, NationalTaxpayerCompanies, NotificationCodes, Transactions, TaxConditions, TaxRateCodes, useDollarRate/useEuroRate</t>
+          <t>useAllExemptions/useExemptionValidation (TSR-124), useAllOtherCharges (TSR-125), useAllDocumentTypes, PharmaceuticalForms, Regimes, NationalTaxpayerCompanies, NotificationCodes, Transactions, TaxConditions, TaxRateCodes, useDollarRate/useEuroRate</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3865,12 +3881,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>TSR-006, TSR-124, TSR-125</t>
+          <t>TSR-124, TSR-125</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Hooks listos sin UI — funcionalidad planeada no terminada</t>
+          <t>Actividades ya vienen de la org registrada; los demás hooks siguen sin UI</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -4042,7 +4058,830 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Funcionalidad</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Incidencia (TSR)</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Bugs / Riesgos</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Prioridad QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tipo de negocio</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>9 tipos + 2 toggles independientes (is_retail_supplier, is_pyme); el BE escribe organization_modules</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>TSR-150</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Los toggles NO son tipos: un minisúper puede ser PYME *y* proveedor de cadena</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Gating de verticales</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>useBusinessType lee la lista de módulos y falla cerrado</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>TSR-150</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>No usa hasModule(): ese falla abierto y auto-concede al owner — correcto para un permiso, incorrecto para un vertical</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding progresivo</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Paso 1 se revela en beats (nombre → tipo → toggles → resumen)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>TSR-150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>El resumen se deriva de BUSINESS_TYPE_MODULES, no de copy fijo</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Pedido manual — 2 tarjetas</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Documento ausente (no colapsado); Pago eliminado; toggle proforma; número editable</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>TSR-151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Punto de entrega sin texto libre: registrado / receptor / cascada CR</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Endpoint pedidos manuales</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>POST /orders discriminado por source; totales recalculados; Idempotency-Key</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>TSR-152</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>El cuerpo del storefront (sin source) sigue validando igual — verificado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SelectField</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Listbox propio, teclado + ARIA; 32 archivos convertidos sin tocar handlers</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>TSR-153</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Un &lt;option&gt; nativo no se puede estilizar; el popup lo dibuja el SO</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Menú 'Más' de pagos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bug de capas CSS: .dropdown-menu fuera de @layer ganaba a las utilities</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TSR-153</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verificado en el CSS compilado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Mesas / cuentas abiertas</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Full-stack; una cuenta de bar es una mesa dinámica</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>TSR-154</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Direccionadas por branch_code entero (TSR-149)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Explotan en componentes al agregar al carrito</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TSR-154</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Un combo con 13% y exento no puede ser una línea plana en un comprobante fiscal</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio 10%</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Línea propia, nunca recargo sobre el total</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>TSR-154</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Se excluye de su propia base o se compone en cada recálculo</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Cuenta dividida</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Por línea o en partes iguales; N documentos</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>TSR-154</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>sharesReconcile verifica que las partes sumen la cuenta original</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Búsqueda por código</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sin gate — cualquier organización</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>TSR-155</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verificado contra datos reales de dev; funciona sin conexión</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Código de balanza</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Peso/precio embebido en EAN-13, parametrizable</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>TSR-155</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>El layout no está estandarizado: cada tienda configura su balanza</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Proformas</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Estado quote, no un tipo de documento</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>TSR-156</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Guarda bloquea quote → delivered: una cotización sin aprobar no debe facturarse</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Puntos de venta manuales</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CRUD junto al importador de Excel</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>TSR-157</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Totales derivados; sobre-asignar devuelve 422 nombrando la línea</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Happy hour</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Ventanas que cruzan medianoche; nunca sube el precio</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TSR-158</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>El servidor re-resuelve al enviar: el reloj del cliente no fija precios fiscales</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Lotes / FEFO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Primero el que vence, no el que llegó</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TSR-159</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Stock sin fecha va al final; 0 días = vence hoy</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Facturación recurrente</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Cadencia con recorte de mes</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>TSR-160</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Genera borrador, nunca transmite; falta EventBridge</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Unidades con conversión</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Stock en rollos, venta por metro</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>TSR-161</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Factor 0 rechazado; price_override gana</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Un módulo, dos verticales (salón y taller)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>TSR-162</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>asset_id nullable: el salón agenda una persona, el taller persona + vehículo</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Órdenes de trabajo</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PM con order_type='work_order'</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>TSR-163</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>No es una entidad nueva; client_assets sí, para historial por activo</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Importación Excel estructurada</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Descuento 07 Comercial + impuestos del producto</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>TSR-152</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Sólo 01/03 desvían IVA a fábrica; 07 debe seguir siendo rebaja de precio</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Ticket 80 mm</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Generado en el backend (ticket.html → wkhtmltopdf → S3)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>TSR-127</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Se descartó imprimir en el navegador: dos maquetadores harían que una reimpresión no coincida con el original</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Ferias</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del selector a propósito</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>❌ Faltante</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>TSR-164</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Es agrupación multi-organización, no un tipo de negocio</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4086,7 +4925,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DocumentActionModal.tsx:13-17,107,151 ('Ver PDF', 'Descargar', 'Reenviar correo'), DocumentTypesFilter.tsx:35 ('Todos los tipos'), ComplexSearchModal.tsx:315 ('Fecha desc (por defecto)'). En EN se ven fragmentos sin traducir. Incluye llaves muertas clients.orders.comingSoon*</t>
+          <t>Resuelto 2026-08-06: acciones, estados, filtros y ordenamiento usan llaves ES/EN; llaves muertas clients.orders.comingSoon* eliminadas</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4257,7 +5096,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Impresión de recibo de venta inalcanzable</t>
+          <t>Impresión de ticket — RESUELTO (backend)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4328,7 +5167,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>public/sw.js reenvía con Bearer ${sale.token} pero useCartFlow nunca persiste token en db.sales → Bearer undefined, el replay falla siempre y la venta queda synced:false para siempre (y el token Cognito expiraría antes de una reconexión típica). El modo offline del POS es efectivamente pérdida de ventas</t>
+          <t>Resuelto 2026-08-06: replay autenticado en primer plano con token fresco, queue Dexie v2, estados/reintentos, aislamiento por usuario e idempotencia org-scoped en sales-be</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4337,8 +5176,74 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TSR-131</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Recibo de checkout perdía totales y cerraba el tab antes del resultado</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-08-06: snapshot previo al clear, recibo confirmado/encolado persistente y cierre del tab únicamente al iniciar Nueva venta</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TSR-132</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Drawers/modales ocultos o recortados por scroll/transform</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-08-06: portal al body, overlay stack, body lock ref-counted, Escape/backdrop topmost, focus trap/restoration, dialog y 100dvh; 3 tests</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TSR-133</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Bundle principal del POS supera 500 KB</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Build 2026-08-06: ~1.49 MB minificado / ~365 KB gzip. Separar rutas/chunks en un trabajo de performance independiente</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D13"/>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4500,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4647,7 +5552,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Condición de venta (catálogo), actividad económica, plazo de crédito, moneda</t>
+          <t>Condición de venta, actividad económica registrada de la org, plazo de crédito, moneda</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4662,7 +5567,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>activity_code='722000' hardcodeado — useAllEconomicActivities existe sin usar</t>
+          <t>Auto-selecciona primera actividad activa; bloquea envío sin actividad configurada</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4807,12 +5712,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Persiste PRIMERO en IndexedDB (db.sales, synced:false), descuenta inventario, POST; en fallo registra Background Sync sync-sales (public/sw.js)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>❌ Faltante</t>
+          <t>Persiste primero en IndexedDB, intenta POST inmediato y reenvía desde la app autenticada al reconectar/iniciar sesión</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4822,7 +5727,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>BUG: sw.js reenvía Bearer ${sale.token} pero useCartFlow nunca guarda token → replay falla siempre; las ventas offline se encolan pero jamás se sincronizan</t>
+          <t>Queue con estados/reintentos + token fresco; Idempotency-Key compartida con sales-be. Probar reconexión real y errores permanentes</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4834,27 +5739,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Cierre de caja</t>
+          <t>Recibo de checkout</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ClosingFlow.tsx (450 líneas, BE con soporte completo)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>❌ Faltante</t>
+          <t>Resultado confirmado o encolado; conserva resumen y tab hasta iniciar Nueva venta</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TSR-005</t>
+          <t>TSR-131</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Componente nunca montado — el ciclo de cajero no se puede cerrar desde la UI</t>
+          <t>Snapshot de total/items previo al clear; probar cierre por botón, Escape y receipt queued</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4866,37 +5771,69 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Cierre de caja</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ClosingFlow.tsx (450 líneas, BE con soporte completo)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>❌ Faltante</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>TSR-005</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Componente nunca montado — el ciclo de cajero no se puede cerrar desde la UI</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Apertura de sesión / turno</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Selección de sesión activa; turno server-side pendiente</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>🟡 Parcial</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>TSR-005</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Turno server-side al iniciar sesión no implementado</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5069,7 +6006,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Strings hardcodeados en español</t>
+          <t>Acciones y estados traducidos ES/EN</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5507,7 +6444,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ClientOrderHistory (real; 'coming soon' quedó como llaves i18n muertas)</t>
+          <t>ClientOrderHistory real</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -5517,12 +6454,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>TSR-119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>useClientOrders.ts sin verificar; llaves clients.orders.comingSoon* muertas</t>
+          <t>useClientOrders.ts sigue sin verificar; llaves comingSoon* eliminadas</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">

--- a/docs/qa/POS_FE_QA_ANALYSIS.xlsx
+++ b/docs/qa/POS_FE_QA_ANALYSIS.xlsx
@@ -53,7 +53,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Catálogos-DataApi'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Código-Huérfano'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Verticales-TipoNegocio'!$A$1:$F$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Hallazgos'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Hallazgos'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -970,7 +970,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2" t="n"/>
     </row>
@@ -1026,7 +1026,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2" t="n"/>
     </row>
@@ -2458,27 +2458,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NotificationsBell + NotificationsContext: niveles, CTA, targeting por app, eventos silenciosos</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>🟡 Parcial</t>
+          <t>Centro persistido por usuario (app_notifications + user_notifications) con push en tiempo real por AppSync Events; el contexto en memoria queda para avisos efímeros de la app</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>✅ Completo</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TSR-128</t>
+          <t>TSR-238 (cierra TSR-128)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100% client-side (useState), se pierde al refrescar; source:'be' existe pero ningún backend publica</t>
+          <t>Hidrata una vez y vive de eventos empujados (staleTime: Infinity, sin refetchInterval). Verificar badge, marcar leída/todas, reconexión y rechazo de canal ajeno</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9 tipos + 2 toggles independientes (is_retail_supplier, is_pyme); el BE escribe organization_modules</t>
+          <t>9 tipos + 2 toggles independientes (is_retail_supplier, is_pyme). Ya no escribe permisos: decide qué promueve la app</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>TSR-150</t>
+          <t>TSR-150 · TSR-240</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>useBusinessType lee la lista de módulos y falla cerrado</t>
+          <t>Eliminado: toda organización tiene todos los módulos. hasVertical solo consulta la preferencia de visibilidad de la org</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TSR-150</t>
+          <t>TSR-240 (revierte el gating de TSR-150)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>No usa hasModule(): ese falla abierto y auto-concede al owner — correcto para un permiso, incorrecto para un vertical</t>
+          <t>El tipo de negocio describe lo que un negocio suele hacer, no lo que le está permitido. Verificar que un minisúper abra Mesas y que los roles ya no dependan del tipo</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>El resumen se deriva de BUSINESS_TYPE_MODULES, no de copy fijo</t>
+          <t>El resumen se deriva de BUSINESS_TYPE_EMPHASIS, no de copy fijo</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Notificaciones sin backend ni persistencia</t>
+          <t>Notificaciones sin backend ni persistencia — RESUELTO por TSR-238</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NotificationsContext 100% client-side (useState) — se pierde al refrescar; source:'be' existe pero nada lo publica; bloquea el feed de invalidación de catálogos</t>
+          <t>Centro de notificaciones persistido (dos tablas: evento vs. estado de lectura por destinatario), lambda user-notifications y push por AppSync Events sin polling. El contexto en memoria queda para avisos efímeros con clave i18n</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -5135,17 +5135,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TSR-129</t>
+          <t>TSR-237</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Dos pipelines de despliegue sin reconciliar</t>
+          <t>Puesto y terminal bloqueaban el POS completo</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>El POS surfacea el pipeline markets-api (pre-deployments→publish→history), nunca ejercitado; el despliegue REAL de sitios org es el provisioner de sales-be (TSR-118 W2, vivo), sin UI en el POS. Decidir cuál superficie el POS y verificar/retirar el otro</t>
+          <t>Resuelto 2026-09-10: eran una precondición a pantalla completa; ahora son dos campos del documento (tarjeta Sucursal y terminal en el checkout), resueltos solos (asignación → selección vigente → primera sucursal con terminal). SessionSetupScreen eliminado</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -5157,17 +5157,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TSR-130</t>
+          <t>TSR-238</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Replay de ventas offline roto (BUG confirmado)</t>
+          <t>Centro de notificaciones en tiempo real</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Resuelto 2026-08-06: replay autenticado en primer plano con token fresco, queue Dexie v2, estados/reintentos, aislamiento por usuario e idempotencia org-scoped en sales-be</t>
+          <t>Resuelto (código) 2026-09-10 — falta desplegar: migración, stack AppSync y VITE_APPSYNC_EVENTS_URL. Ver roadmap §7 paso 14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TSR-131</t>
+          <t>TSR-239</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Recibo de checkout perdía totales y cerraba el tab antes del resultado</t>
+          <t>El veredicto de Hacienda no llegaba a quien emitió</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Resuelto 2026-08-06: snapshot previo al clear, recibo confirmado/encolado persistente y cierre del tab únicamente al iniciar Nueva venta</t>
+          <t>Resuelto (código) 2026-09-10: aceptado/rechazado se notifica al emisor con los motivos de Hacienda y el clic abre el detalle del documento</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -5201,17 +5201,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TSR-132</t>
+          <t>TSR-240</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Drawers/modales ocultos o recortados por scroll/transform</t>
+          <t>El tipo de negocio limitaba funciones y roles</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Resuelto 2026-08-06: portal al body, overlay stack, body lock ref-counted, Escape/backdrop topmost, focus trap/restoration, dialog y 100dvh; 3 tests</t>
+          <t>Resuelto (código) 2026-09-10: todas las orgs tienen todos los módulos; el tipo solo decide qué se promueve. Ocultar una superficie pasa a ser preferencia reversible de la org. Requiere re-ejecutar db:seed:org-modules</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -5223,27 +5223,181 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>TSR-241</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Facturar un pedido dejaba vacíos departamento y punto de entrega</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-09-10: el pedido trae códigos (department_code, gln) y los selects van por UUID; ahora se resuelven los ids contra las listas y se escriben de vuelta en el formulario</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TSR-242</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Escribir en un select abierto no buscaba</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-09-10: el filtro solo existía con &gt;=8 opciones; ahora escribir filtra siempre y revela el cuadro de búsqueda</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TSR-243</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>El desplegable de CABYS no aparecía en el formulario de producto</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-09-10: la busqueda si corria y los resultados si se pintaban, detras del drawer. Ambos selectores portaban a body con z-popover (80) mientras el formulario es un Drawer en z-drawer (200). Ahora usan OverlayPortal en z-drawer-modal y posicion fixed que sobrevive al scroll del drawer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TSR-129</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dos pipelines de despliegue sin reconciliar</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>El POS surfacea el pipeline markets-api (pre-deployments→publish→history), nunca ejercitado; el despliegue REAL de sitios org es el provisioner de sales-be (TSR-118 W2, vivo), sin UI en el POS. Decidir cuál superficie el POS y verificar/retirar el otro</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TSR-130</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Replay de ventas offline roto (BUG confirmado)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-08-06: replay autenticado en primer plano con token fresco, queue Dexie v2, estados/reintentos, aislamiento por usuario e idempotencia org-scoped en sales-be</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TSR-131</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Recibo de checkout perdía totales y cerraba el tab antes del resultado</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-08-06: snapshot previo al clear, recibo confirmado/encolado persistente y cierre del tab únicamente al iniciar Nueva venta</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TSR-132</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Drawers/modales ocultos o recortados por scroll/transform</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Resuelto 2026-08-06: portal al body, overlay stack, body lock ref-counted, Escape/backdrop topmost, focus trap/restoration, dialog y 100dvh; 3 tests</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>TSR-133</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Bundle principal del POS supera 500 KB</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Build 2026-08-06: ~1.49 MB minificado / ~365 KB gzip. Separar rutas/chunks en un trabajo de performance independiente</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
